--- a/Modules/CVMod8_V2/CVMod8_V2_BOM.xlsx
+++ b/Modules/CVMod8_V2/CVMod8_V2_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\CVMod8_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077031D6-058E-4C5F-9902-ACF7108DD09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D30F47E-725E-4DDA-9DF0-3CAD3C8D5E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,15 +125,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>M2 Screw</t>
   </si>
   <si>
@@ -281,9 +275,6 @@
     <t>https://www.tme.eu/de/en/details/l-937egw/tht-leds-3mm/kingbright-electronic/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.tme.eu/de/en/details/tfm-m2x10_dr211of/metal-spacers/dremec/211x10of/</t>
   </si>
   <si>
@@ -672,6 +663,15 @@
   </si>
   <si>
     <t>Avalon Harmonics CVMod8 V2</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1575,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1610,19 +1610,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1633,19 +1633,19 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
         <v>76</v>
       </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -1657,19 +1657,19 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1680,19 +1680,19 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1700,22 +1700,22 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1726,19 +1726,19 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1746,22 +1746,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1769,22 +1769,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1795,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>21</v>
@@ -1812,22 +1812,22 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1838,19 +1838,19 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1858,22 +1858,22 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1881,22 +1881,22 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1904,13 +1904,13 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
@@ -1919,7 +1919,7 @@
         <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1930,7 +1930,7 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1939,10 +1939,10 @@
         <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="J17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1950,19 +1950,19 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1970,19 +1970,19 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
         <v>49</v>
       </c>
-      <c r="C20" t="s">
+      <c r="F20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1990,19 +1990,19 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2019,13 +2019,13 @@
         <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="J23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2033,19 +2033,19 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2065,7 +2065,7 @@
         <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2076,7 +2076,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
         <v>26</v>
@@ -2085,12 +2085,12 @@
         <v>28</v>
       </c>
       <c r="J26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2098,32 +2098,32 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2141,24 +2141,24 @@
     <hyperlink ref="F16" r:id="rId2" xr:uid="{132D58BF-3722-4009-997D-85D83E0427E1}"/>
     <hyperlink ref="F11" r:id="rId3" xr:uid="{8566253D-4BC4-4E88-AEC8-42702836E845}"/>
     <hyperlink ref="F25" r:id="rId4" xr:uid="{F21785D4-9E60-49FA-B073-FBF9DF240B91}"/>
-    <hyperlink ref="F23" r:id="rId5" xr:uid="{95AE4A90-92CF-45E8-81B2-053915D45020}"/>
-    <hyperlink ref="F24" r:id="rId6" xr:uid="{21D8AB96-92BC-4134-9A7C-8F0559A3B677}"/>
-    <hyperlink ref="F26" r:id="rId7" xr:uid="{01A30E79-E5B2-47BA-A3E7-2780BB7C6150}"/>
-    <hyperlink ref="F15" r:id="rId8" xr:uid="{6A2C0C52-D1AE-4FD1-A752-B35B8C35F326}"/>
-    <hyperlink ref="F19" r:id="rId9" xr:uid="{4950D606-84F3-4140-9E5E-B30237872926}"/>
-    <hyperlink ref="F20" r:id="rId10" xr:uid="{598DC950-F0D5-4E2E-8295-A9654732F752}"/>
-    <hyperlink ref="F14" r:id="rId11" xr:uid="{85CF4EAD-C815-4764-99B0-3CD3F7C65648}"/>
-    <hyperlink ref="F17" r:id="rId12" xr:uid="{E5E643F1-584B-4524-8FC0-A33A6B86DA13}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{F9D4FE49-B4B1-48B5-AA25-31D2A78EB9EB}"/>
-    <hyperlink ref="F21" r:id="rId14" xr:uid="{C4F7CA67-414F-44EB-8D12-BDA7608A9909}"/>
-    <hyperlink ref="F7" r:id="rId15" xr:uid="{50D31F83-0CC7-4366-B19A-AB742DEC9C95}"/>
-    <hyperlink ref="F8" r:id="rId16" xr:uid="{8A08C8AB-0BC2-48C9-839C-9A1FF04B94D0}"/>
-    <hyperlink ref="F6" r:id="rId17" xr:uid="{8CB4637D-11ED-44D2-995C-63FD7A7880CC}"/>
-    <hyperlink ref="F5" r:id="rId18" xr:uid="{950D2F1D-A663-4192-B413-DEF807105565}"/>
-    <hyperlink ref="F3" r:id="rId19" xr:uid="{148C00D5-077D-40A7-90B4-A86DC721AC43}"/>
-    <hyperlink ref="F9" r:id="rId20" xr:uid="{4B8DCC33-CC14-4260-9B2A-502EFE5C16D7}"/>
-    <hyperlink ref="F10" r:id="rId21" xr:uid="{0985F146-BC4A-4DC8-A796-B9EBFBBF916A}"/>
-    <hyperlink ref="F4" r:id="rId22" xr:uid="{39108D5A-B9E3-49BD-8858-806D8CB46293}"/>
+    <hyperlink ref="F26" r:id="rId5" xr:uid="{01A30E79-E5B2-47BA-A3E7-2780BB7C6150}"/>
+    <hyperlink ref="F15" r:id="rId6" xr:uid="{6A2C0C52-D1AE-4FD1-A752-B35B8C35F326}"/>
+    <hyperlink ref="F19" r:id="rId7" xr:uid="{4950D606-84F3-4140-9E5E-B30237872926}"/>
+    <hyperlink ref="F20" r:id="rId8" xr:uid="{598DC950-F0D5-4E2E-8295-A9654732F752}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{85CF4EAD-C815-4764-99B0-3CD3F7C65648}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{F9D4FE49-B4B1-48B5-AA25-31D2A78EB9EB}"/>
+    <hyperlink ref="F21" r:id="rId11" xr:uid="{C4F7CA67-414F-44EB-8D12-BDA7608A9909}"/>
+    <hyperlink ref="F7" r:id="rId12" xr:uid="{50D31F83-0CC7-4366-B19A-AB742DEC9C95}"/>
+    <hyperlink ref="F8" r:id="rId13" xr:uid="{8A08C8AB-0BC2-48C9-839C-9A1FF04B94D0}"/>
+    <hyperlink ref="F6" r:id="rId14" xr:uid="{8CB4637D-11ED-44D2-995C-63FD7A7880CC}"/>
+    <hyperlink ref="F5" r:id="rId15" xr:uid="{950D2F1D-A663-4192-B413-DEF807105565}"/>
+    <hyperlink ref="F3" r:id="rId16" xr:uid="{148C00D5-077D-40A7-90B4-A86DC721AC43}"/>
+    <hyperlink ref="F9" r:id="rId17" xr:uid="{4B8DCC33-CC14-4260-9B2A-502EFE5C16D7}"/>
+    <hyperlink ref="F10" r:id="rId18" xr:uid="{0985F146-BC4A-4DC8-A796-B9EBFBBF916A}"/>
+    <hyperlink ref="F4" r:id="rId19" xr:uid="{39108D5A-B9E3-49BD-8858-806D8CB46293}"/>
+    <hyperlink ref="F23" r:id="rId20" xr:uid="{AEA1F756-EF32-4E1F-A63D-D604B8E9A1DB}"/>
+    <hyperlink ref="F24" r:id="rId21" xr:uid="{BE2B6FA2-AF87-4638-A8E6-0E96554BC915}"/>
+    <hyperlink ref="F17" r:id="rId22" xr:uid="{255919DE-5043-47DE-8032-3A0AD3AF059F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
